--- a/samples/bakery-full.xlsx
+++ b/samples/bakery-full.xlsx
@@ -2564,8 +2564,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="21639315"/>
-        <c:axId val="45316053"/>
+        <c:axId val="86665613"/>
+        <c:axId val="94487251"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2674,11 +2674,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="65221434"/>
-        <c:axId val="85174983"/>
+        <c:axId val="98078931"/>
+        <c:axId val="29715370"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21639315"/>
+        <c:axId val="86665613"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2710,7 +2710,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45316053"/>
+        <c:crossAx val="94487251"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2718,7 +2718,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45316053"/>
+        <c:axId val="94487251"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2757,12 +2757,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21639315"/>
+        <c:crossAx val="86665613"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="65221434"/>
+        <c:axId val="98078931"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2794,7 +2794,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85174983"/>
+        <c:crossAx val="29715370"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2802,7 +2802,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85174983"/>
+        <c:axId val="29715370"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2831,7 +2831,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65221434"/>
+        <c:crossAx val="98078931"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3220,11 +3220,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="30497433"/>
-        <c:axId val="39338835"/>
+        <c:axId val="77073757"/>
+        <c:axId val="81488987"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30497433"/>
+        <c:axId val="77073757"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3256,7 +3256,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39338835"/>
+        <c:crossAx val="81488987"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3264,7 +3264,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39338835"/>
+        <c:axId val="81488987"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3303,7 +3303,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30497433"/>
+        <c:crossAx val="77073757"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3559,7 +3559,7 @@
                   <c:v>0.462712266442819</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.361999900076399</c:v>
+                  <c:v>0.361999900076398</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3567,11 +3567,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="17480798"/>
-        <c:axId val="489789"/>
+        <c:axId val="63594207"/>
+        <c:axId val="51874956"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17480798"/>
+        <c:axId val="63594207"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3603,7 +3603,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="489789"/>
+        <c:crossAx val="51874956"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3611,7 +3611,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="489789"/>
+        <c:axId val="51874956"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3650,7 +3650,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17480798"/>
+        <c:crossAx val="63594207"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3830,8 +3830,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="8560732"/>
-        <c:axId val="36781019"/>
+        <c:axId val="57391084"/>
+        <c:axId val="691444"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -3940,11 +3940,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="7653466"/>
-        <c:axId val="52699159"/>
+        <c:axId val="2819432"/>
+        <c:axId val="97182005"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8560732"/>
+        <c:axId val="57391084"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3976,7 +3976,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36781019"/>
+        <c:crossAx val="691444"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3984,7 +3984,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36781019"/>
+        <c:axId val="691444"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4023,12 +4023,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8560732"/>
+        <c:crossAx val="57391084"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="7653466"/>
+        <c:axId val="2819432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4060,7 +4060,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52699159"/>
+        <c:crossAx val="97182005"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4068,7 +4068,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="52699159"/>
+        <c:axId val="97182005"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4097,7 +4097,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7653466"/>
+        <c:crossAx val="2819432"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4361,8 +4361,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="20122864"/>
-        <c:axId val="99271888"/>
+        <c:axId val="75533306"/>
+        <c:axId val="33277539"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -4471,11 +4471,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="87722719"/>
-        <c:axId val="52042852"/>
+        <c:axId val="19671995"/>
+        <c:axId val="11752761"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="20122864"/>
+        <c:axId val="75533306"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4507,7 +4507,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99271888"/>
+        <c:crossAx val="33277539"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4515,7 +4515,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99271888"/>
+        <c:axId val="33277539"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4554,12 +4554,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20122864"/>
+        <c:crossAx val="75533306"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="87722719"/>
+        <c:axId val="19671995"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4591,7 +4591,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52042852"/>
+        <c:crossAx val="11752761"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4599,7 +4599,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="52042852"/>
+        <c:axId val="11752761"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4628,7 +4628,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87722719"/>
+        <c:crossAx val="19671995"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4976,11 +4976,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="64707417"/>
-        <c:axId val="83262341"/>
+        <c:axId val="4535387"/>
+        <c:axId val="45527121"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="64707417"/>
+        <c:axId val="4535387"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5012,7 +5012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83262341"/>
+        <c:crossAx val="45527121"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5020,7 +5020,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83262341"/>
+        <c:axId val="45527121"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5059,7 +5059,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64707417"/>
+        <c:crossAx val="4535387"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5243,11 +5243,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="97790610"/>
-        <c:axId val="90887379"/>
+        <c:axId val="40301446"/>
+        <c:axId val="27053232"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97790610"/>
+        <c:axId val="40301446"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5279,7 +5279,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90887379"/>
+        <c:crossAx val="27053232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5287,7 +5287,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90887379"/>
+        <c:axId val="27053232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5326,7 +5326,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97790610"/>
+        <c:crossAx val="40301446"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5566,11 +5566,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="20128966"/>
-        <c:axId val="61685927"/>
+        <c:axId val="31621073"/>
+        <c:axId val="18369405"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="20128966"/>
+        <c:axId val="31621073"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5602,7 +5602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61685927"/>
+        <c:crossAx val="18369405"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5610,7 +5610,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61685927"/>
+        <c:axId val="18369405"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5649,7 +5649,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20128966"/>
+        <c:crossAx val="31621073"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5883,8 +5883,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="39943034"/>
-        <c:axId val="19578444"/>
+        <c:axId val="77617565"/>
+        <c:axId val="32946447"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6197,11 +6197,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="39943034"/>
-        <c:axId val="19578444"/>
+        <c:axId val="77617565"/>
+        <c:axId val="32946447"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39943034"/>
+        <c:axId val="77617565"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6233,7 +6233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19578444"/>
+        <c:crossAx val="32946447"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6241,7 +6241,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19578444"/>
+        <c:axId val="32946447"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6280,7 +6280,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39943034"/>
+        <c:crossAx val="77617565"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6790,8 +6790,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="23549332"/>
-        <c:axId val="49393411"/>
+        <c:axId val="83274639"/>
+        <c:axId val="39959674"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -6954,11 +6954,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="29776023"/>
-        <c:axId val="70565660"/>
+        <c:axId val="37123405"/>
+        <c:axId val="221777"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="23549332"/>
+        <c:axId val="83274639"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6990,7 +6990,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49393411"/>
+        <c:crossAx val="39959674"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6998,7 +6998,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49393411"/>
+        <c:axId val="39959674"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7037,12 +7037,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23549332"/>
+        <c:crossAx val="83274639"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="29776023"/>
+        <c:axId val="37123405"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7074,7 +7074,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70565660"/>
+        <c:crossAx val="221777"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7082,7 +7082,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70565660"/>
+        <c:axId val="221777"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7111,7 +7111,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29776023"/>
+        <c:crossAx val="37123405"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7621,8 +7621,8 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="100"/>
-        <c:axId val="21936656"/>
-        <c:axId val="64778703"/>
+        <c:axId val="8272053"/>
+        <c:axId val="3381"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="stacked"/>
@@ -7785,11 +7785,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="21936656"/>
-        <c:axId val="64778703"/>
+        <c:axId val="8272053"/>
+        <c:axId val="3381"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="21936656"/>
+        <c:axId val="8272053"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7821,7 +7821,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64778703"/>
+        <c:crossAx val="3381"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7829,7 +7829,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64778703"/>
+        <c:axId val="3381"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7868,7 +7868,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21936656"/>
+        <c:crossAx val="8272053"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8296,11 +8296,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="41054673"/>
-        <c:axId val="28080260"/>
+        <c:axId val="22575639"/>
+        <c:axId val="57913811"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41054673"/>
+        <c:axId val="22575639"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -8332,7 +8332,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28080260"/>
+        <c:crossAx val="57913811"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8340,7 +8340,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28080260"/>
+        <c:axId val="57913811"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8379,7 +8379,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41054673"/>
+        <c:crossAx val="22575639"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12158,147 +12158,147 @@
         <v>355</v>
       </c>
       <c r="C26" s="52" t="n">
-        <f aca="false">-C14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-C14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-1962.21805714286</v>
       </c>
       <c r="D26" s="52" t="n">
-        <f aca="false">-D14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-D14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2071.23017142857</v>
       </c>
       <c r="E26" s="52" t="n">
-        <f aca="false">-E14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-E14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2180.24228571429</v>
       </c>
       <c r="F26" s="52" t="n">
-        <f aca="false">-F14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-F14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2180.24228571429</v>
       </c>
       <c r="G26" s="52" t="n">
-        <f aca="false">-G14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-G14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2180.24228571429</v>
       </c>
       <c r="H26" s="52" t="n">
-        <f aca="false">-H14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-H14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2180.24228571429</v>
       </c>
       <c r="I26" s="52" t="n">
-        <f aca="false">-I14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-I14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2180.24228571429</v>
       </c>
       <c r="J26" s="52" t="n">
-        <f aca="false">-J14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-J14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2180.24228571429</v>
       </c>
       <c r="K26" s="52" t="n">
-        <f aca="false">-K14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-K14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2180.24228571429</v>
       </c>
       <c r="L26" s="52" t="n">
-        <f aca="false">-L14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-L14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2180.24228571429</v>
       </c>
       <c r="M26" s="52" t="n">
-        <f aca="false">-M14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-M14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2725.30285714286</v>
       </c>
       <c r="N26" s="52" t="n">
-        <f aca="false">-N14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-N14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2725.30285714286</v>
       </c>
       <c r="O26" s="52" t="n">
-        <f aca="false">-O14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-O14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="P26" s="52" t="n">
-        <f aca="false">-P14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-P14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="Q26" s="52" t="n">
-        <f aca="false">-Q14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-Q14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="R26" s="52" t="n">
-        <f aca="false">-R14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-R14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="S26" s="52" t="n">
-        <f aca="false">-S14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-S14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="T26" s="52" t="n">
-        <f aca="false">-T14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-T14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="U26" s="52" t="n">
-        <f aca="false">-U14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-U14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="V26" s="52" t="n">
-        <f aca="false">-V14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-V14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="W26" s="52" t="n">
-        <f aca="false">-W14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-W14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="X26" s="52" t="n">
-        <f aca="false">-X14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-X14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2313.01904091429</v>
       </c>
       <c r="Y26" s="52" t="n">
-        <f aca="false">-Y14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-Y14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2891.27380114286</v>
       </c>
       <c r="Z26" s="52" t="n">
-        <f aca="false">-Z14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-Z14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2891.27380114286</v>
       </c>
       <c r="AA26" s="52" t="n">
-        <f aca="false">-AA14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AA14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AB26" s="52" t="n">
-        <f aca="false">-AB14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AB14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AC26" s="52" t="n">
-        <f aca="false">-AC14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AC14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AD26" s="52" t="n">
-        <f aca="false">-AD14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AD14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AE26" s="52" t="n">
-        <f aca="false">-AE14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AE14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AF26" s="52" t="n">
-        <f aca="false">-AF14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AF14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AG26" s="52" t="n">
-        <f aca="false">-AG14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AG14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AH26" s="52" t="n">
-        <f aca="false">-AH14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AH14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AI26" s="52" t="n">
-        <f aca="false">-AI14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AI14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AJ26" s="52" t="n">
-        <f aca="false">-AJ14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AJ14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-2453.88190050597</v>
       </c>
       <c r="AK26" s="52" t="n">
-        <f aca="false">-AK14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AK14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-3067.35237563246</v>
       </c>
       <c r="AL26" s="52" t="n">
-        <f aca="false">-AL14*Inputs!$E$24*Inputs!$E$26/MAX(0.01,1-Inputs!$E$26)</f>
+        <f aca="false">-AL14*Inputs!$E$24*Inputs!$E$26*100/MAX(1,100-100*Inputs!$E$26)</f>
         <v>-3067.35237563246</v>
       </c>
     </row>
@@ -14341,11 +14341,11 @@
       </c>
       <c r="Q44" s="58" t="n">
         <f aca="false">Q41+Q55</f>
-        <v>12341.9074613638</v>
+        <v>12341.9074613639</v>
       </c>
       <c r="R44" s="58" t="n">
         <f aca="false">R41+R55</f>
-        <v>12328.0185724749</v>
+        <v>12328.018572475</v>
       </c>
       <c r="S44" s="58" t="n">
         <f aca="false">S41+S55</f>
@@ -14651,7 +14651,7 @@
       </c>
       <c r="T46" s="53" t="n">
         <f aca="false">T44+T45</f>
-        <v>11889.4074613638</v>
+        <v>11889.4074613639</v>
       </c>
       <c r="U46" s="53" t="n">
         <f aca="false">U44+U45</f>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="V46" s="53" t="n">
         <f aca="false">V44+V45</f>
-        <v>11880.5185724749</v>
+        <v>11880.518572475</v>
       </c>
       <c r="W46" s="53" t="n">
         <f aca="false">W44+W45</f>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="AI47" s="52" t="n">
         <f aca="false">AH47+AI46</f>
-        <v>436317.984699272</v>
+        <v>436317.984699273</v>
       </c>
       <c r="AJ47" s="52" t="n">
         <f aca="false">AI47+AJ46</f>
@@ -15009,7 +15009,7 @@
       </c>
       <c r="AI48" s="52" t="n">
         <f aca="false">MAX(AH48,AI47)</f>
-        <v>436317.984699272</v>
+        <v>436317.984699273</v>
       </c>
       <c r="AJ48" s="52" t="n">
         <f aca="false">MAX(AI48,AJ47)</f>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="Q49" s="52" t="n">
         <f aca="false">-(Q48-P48)*Inputs!$E$70</f>
-        <v>-2499.5755668864</v>
+        <v>-2499.57556688641</v>
       </c>
       <c r="R49" s="52" t="n">
         <f aca="false">-(R48-Q48)*Inputs!$E$70</f>
@@ -15098,11 +15098,11 @@
       </c>
       <c r="T49" s="52" t="n">
         <f aca="false">-(T48-S48)*Inputs!$E$70</f>
-        <v>-2496.7755668864</v>
+        <v>-2496.77556688641</v>
       </c>
       <c r="U49" s="52" t="n">
         <f aca="false">-(U48-T48)*Inputs!$E$70</f>
-        <v>-2495.84223355307</v>
+        <v>-2495.84223355308</v>
       </c>
       <c r="V49" s="52" t="n">
         <f aca="false">-(V48-U48)*Inputs!$E$70</f>
@@ -15227,7 +15227,7 @@
       </c>
       <c r="O50" s="53" t="n">
         <f aca="false">O46+O49</f>
-        <v>9410.18745003298</v>
+        <v>9410.187450033</v>
       </c>
       <c r="P50" s="53" t="n">
         <f aca="false">P46+P49</f>
@@ -15239,31 +15239,31 @@
       </c>
       <c r="R50" s="53" t="n">
         <f aca="false">R46+R49</f>
-        <v>9399.65411669965</v>
+        <v>9399.65411669967</v>
       </c>
       <c r="S50" s="53" t="n">
         <f aca="false">S46+S49</f>
-        <v>9396.14300558854</v>
+        <v>9396.14300558855</v>
       </c>
       <c r="T50" s="53" t="n">
         <f aca="false">T46+T49</f>
-        <v>9392.63189447743</v>
+        <v>9392.63189447744</v>
       </c>
       <c r="U50" s="53" t="n">
         <f aca="false">U46+U49</f>
-        <v>9389.12078336632</v>
+        <v>9389.12078336633</v>
       </c>
       <c r="V50" s="53" t="n">
         <f aca="false">V46+V49</f>
-        <v>9385.60967225521</v>
+        <v>9385.60967225522</v>
       </c>
       <c r="W50" s="53" t="n">
         <f aca="false">W46+W49</f>
-        <v>9382.09856114409</v>
+        <v>9382.09856114411</v>
       </c>
       <c r="X50" s="53" t="n">
         <f aca="false">X46+X49</f>
-        <v>9378.58745003298</v>
+        <v>9378.587450033</v>
       </c>
       <c r="Y50" s="53" t="n">
         <f aca="false">Y46+Y49</f>
@@ -17373,7 +17373,7 @@
       </c>
       <c r="O70" s="52" t="n">
         <f aca="false">N67-O67</f>
-        <v>308.982288822856</v>
+        <v>308.982288822857</v>
       </c>
       <c r="P70" s="52" t="n">
         <f aca="false">O67-P67</f>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="Y70" s="52" t="n">
         <f aca="false">X67-Y67</f>
-        <v>-727.771095222857</v>
+        <v>-727.771095222858</v>
       </c>
       <c r="Z70" s="52" t="n">
         <f aca="false">Y67-Z67</f>
@@ -17727,7 +17727,7 @@
       </c>
       <c r="X74" s="58" t="n">
         <f aca="false">X50-X55+X69+X70+X71</f>
-        <v>10588.9049103504</v>
+        <v>10588.9049103505</v>
       </c>
       <c r="Y74" s="58" t="n">
         <f aca="false">Y50-Y55+Y69+Y70+Y71</f>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="O78" s="53" t="n">
         <f aca="false">O74+O75+O77</f>
-        <v>9161.59557823615</v>
+        <v>9161.59557823617</v>
       </c>
       <c r="P78" s="53" t="n">
         <f aca="false">P74+P75+P77</f>
@@ -18295,19 +18295,19 @@
       </c>
       <c r="Q78" s="53" t="n">
         <f aca="false">Q74+Q75+Q77</f>
-        <v>8016.260465906</v>
+        <v>8016.26046590601</v>
       </c>
       <c r="R78" s="53" t="n">
         <f aca="false">R74+R75+R77</f>
-        <v>8026.63824368378</v>
+        <v>8026.63824368379</v>
       </c>
       <c r="S78" s="53" t="n">
         <f aca="false">S74+S75+S77</f>
-        <v>8037.01602146156</v>
+        <v>8037.01602146157</v>
       </c>
       <c r="T78" s="53" t="n">
         <f aca="false">T74+T75+T77</f>
-        <v>8047.39379923934</v>
+        <v>8047.39379923935</v>
       </c>
       <c r="U78" s="53" t="n">
         <f aca="false">U74+U75+U77</f>
@@ -18315,15 +18315,15 @@
       </c>
       <c r="V78" s="53" t="n">
         <f aca="false">V74+V75+V77</f>
-        <v>8068.14935479489</v>
+        <v>8068.14935479491</v>
       </c>
       <c r="W78" s="53" t="n">
         <f aca="false">W74+W75+W77</f>
-        <v>8078.52713257267</v>
+        <v>8078.52713257268</v>
       </c>
       <c r="X78" s="53" t="n">
         <f aca="false">X74+X75+X77</f>
-        <v>8088.90491035044</v>
+        <v>8088.90491035046</v>
       </c>
       <c r="Y78" s="53" t="n">
         <f aca="false">Y74+Y75+Y77</f>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="AE79" s="52" t="n">
         <f aca="false">AD80</f>
-        <v>301399.202882855</v>
+        <v>301399.202882856</v>
       </c>
       <c r="AF79" s="52" t="n">
         <f aca="false">AE80</f>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="AD80" s="53" t="n">
         <f aca="false">AD79+AD78</f>
-        <v>301399.202882855</v>
+        <v>301399.202882856</v>
       </c>
       <c r="AE80" s="53" t="n">
         <f aca="false">AE79+AE78</f>
@@ -19056,39 +19056,39 @@
       </c>
       <c r="P85" s="52" t="n">
         <f aca="false">P74+P75</f>
-        <v>9339.21602146156</v>
+        <v>9339.21602146157</v>
       </c>
       <c r="Q85" s="52" t="n">
         <f aca="false">Q74+Q75</f>
-        <v>9349.59379923934</v>
+        <v>9349.59379923935</v>
       </c>
       <c r="R85" s="52" t="n">
         <f aca="false">R74+R75</f>
-        <v>9359.97157701711</v>
+        <v>9359.97157701713</v>
       </c>
       <c r="S85" s="52" t="n">
         <f aca="false">S74+S75</f>
-        <v>9370.34935479489</v>
+        <v>9370.3493547949</v>
       </c>
       <c r="T85" s="52" t="n">
         <f aca="false">T74+T75</f>
-        <v>9380.72713257267</v>
+        <v>9380.72713257268</v>
       </c>
       <c r="U85" s="52" t="n">
         <f aca="false">U74+U75</f>
-        <v>9391.10491035045</v>
+        <v>9391.10491035046</v>
       </c>
       <c r="V85" s="52" t="n">
         <f aca="false">V74+V75</f>
-        <v>9401.48268812822</v>
+        <v>9401.48268812824</v>
       </c>
       <c r="W85" s="52" t="n">
         <f aca="false">W74+W75</f>
-        <v>9411.860465906</v>
+        <v>9411.86046590602</v>
       </c>
       <c r="X85" s="52" t="n">
         <f aca="false">X74+X75</f>
-        <v>9422.23824368378</v>
+        <v>9422.23824368379</v>
       </c>
       <c r="Y85" s="52" t="n">
         <f aca="false">Y74+Y75</f>
@@ -19205,7 +19205,7 @@
       </c>
       <c r="P86" s="52" t="n">
         <f aca="false">O86+P85</f>
-        <v>31198.1019696533</v>
+        <v>31198.1019696534</v>
       </c>
       <c r="Q86" s="52" t="n">
         <f aca="false">P86+Q85</f>
@@ -19225,15 +19225,15 @@
       </c>
       <c r="U86" s="52" t="n">
         <f aca="false">T86+U85</f>
-        <v>78049.8487436278</v>
+        <v>78049.8487436279</v>
       </c>
       <c r="V86" s="52" t="n">
         <f aca="false">U86+V85</f>
-        <v>87451.331431756</v>
+        <v>87451.3314317561</v>
       </c>
       <c r="W86" s="52" t="n">
         <f aca="false">V86+W85</f>
-        <v>96863.191897662</v>
+        <v>96863.1918976621</v>
       </c>
       <c r="X86" s="52" t="n">
         <f aca="false">W86+X85</f>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="Y86" s="52" t="n">
         <f aca="false">X86+Y85</f>
-        <v>126245.039325131</v>
+        <v>126245.039325132</v>
       </c>
       <c r="Z86" s="52" t="n">
         <f aca="false">Y86+Z85</f>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="AB86" s="52" t="n">
         <f aca="false">AA86+AB85</f>
-        <v>173414.12805599</v>
+        <v>173414.128055991</v>
       </c>
       <c r="AC86" s="52" t="n">
         <f aca="false">AB86+AC85</f>
@@ -19265,7 +19265,7 @@
       </c>
       <c r="AE86" s="52" t="n">
         <f aca="false">AD86+AE85</f>
-        <v>209407.306962954</v>
+        <v>209407.306962955</v>
       </c>
       <c r="AF86" s="52" t="n">
         <f aca="false">AE86+AF85</f>
@@ -19660,11 +19660,11 @@
       </c>
       <c r="R89" s="52" t="n">
         <f aca="false">R74-R45*(1-Inputs!$E$70)+R75</f>
-        <v>9699.45213257267</v>
+        <v>9699.45213257268</v>
       </c>
       <c r="S89" s="52" t="n">
         <f aca="false">S74-S45*(1-Inputs!$E$70)+S75</f>
-        <v>9702.36879923933</v>
+        <v>9702.36879923935</v>
       </c>
       <c r="T89" s="52" t="n">
         <f aca="false">T74-T45*(1-Inputs!$E$70)+T75</f>
@@ -19672,19 +19672,19 @@
       </c>
       <c r="U89" s="52" t="n">
         <f aca="false">U74-U45*(1-Inputs!$E$70)+U75</f>
-        <v>9708.20213257267</v>
+        <v>9708.20213257268</v>
       </c>
       <c r="V89" s="52" t="n">
         <f aca="false">V74-V45*(1-Inputs!$E$70)+V75</f>
-        <v>9711.11879923934</v>
+        <v>9711.11879923935</v>
       </c>
       <c r="W89" s="52" t="n">
         <f aca="false">W74-W45*(1-Inputs!$E$70)+W75</f>
-        <v>9714.035465906</v>
+        <v>9714.03546590602</v>
       </c>
       <c r="X89" s="52" t="n">
         <f aca="false">X74-X45*(1-Inputs!$E$70)+X75</f>
-        <v>9716.95213257267</v>
+        <v>9716.95213257268</v>
       </c>
       <c r="Y89" s="52" t="n">
         <f aca="false">Y74-Y45*(1-Inputs!$E$70)+Y75</f>
@@ -20203,7 +20203,7 @@
       </c>
       <c r="AK94" s="58" t="n">
         <f aca="false">AK80+AK66+AK67+AK57</f>
-        <v>510466.32721347</v>
+        <v>510466.327213471</v>
       </c>
       <c r="AL94" s="58" t="n">
         <f aca="false">AL80+AL66+AL67+AL57</f>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="X97" s="58" t="n">
         <f aca="false">X95+X96</f>
-        <v>332919.725232586</v>
+        <v>332919.725232587</v>
       </c>
       <c r="Y97" s="58" t="n">
         <f aca="false">Y95+Y96</f>
@@ -20626,7 +20626,7 @@
       </c>
       <c r="AE97" s="58" t="n">
         <f aca="false">AE95+AE96</f>
-        <v>429365.92851593</v>
+        <v>429365.928515931</v>
       </c>
       <c r="AF97" s="58" t="n">
         <f aca="false">AF95+AF96</f>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="AI97" s="58" t="n">
         <f aca="false">AI95+AI96</f>
-        <v>471466.40832839</v>
+        <v>471466.408328391</v>
       </c>
       <c r="AJ97" s="58" t="n">
         <f aca="false">AJ95+AJ96</f>
@@ -27403,7 +27403,7 @@
       </c>
       <c r="C13" s="72" t="n">
         <f aca="false">IF(('Balance Sheet'!C12-'Balance Sheet'!C11)&lt;=0,"n/a",('Balance Sheet'!C5+'Balance Sheet'!C6+'Balance Sheet'!C7)/('Balance Sheet'!C12-'Balance Sheet'!C11))</f>
-        <v>9.62897283771879</v>
+        <v>9.6289728377188</v>
       </c>
       <c r="D13" s="72" t="n">
         <f aca="false">IF(('Balance Sheet'!D12-'Balance Sheet'!D11)&lt;=0,"n/a",('Balance Sheet'!D5+'Balance Sheet'!D6+'Balance Sheet'!D7)/('Balance Sheet'!D12-'Balance Sheet'!D11))</f>
@@ -27461,7 +27461,7 @@
       </c>
       <c r="D16" s="40" t="n">
         <f aca="false">IF('Balance Sheet'!D15&lt;=0,"n/a",'P&amp;L'!D25/'Balance Sheet'!D15)</f>
-        <v>0.361999900076399</v>
+        <v>0.361999900076398</v>
       </c>
       <c r="E16" s="71"/>
     </row>
@@ -27550,7 +27550,7 @@
       </c>
       <c r="D23" s="74" t="n">
         <f aca="false">IF(AND(ISNUMBER(D20),ISNUMBER(D21),ISNUMBER(D22)),D20*D21*D22,"n/a")</f>
-        <v>0.361999900076399</v>
+        <v>0.361999900076398</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
